--- a/hira_material_automation/output/monthly/202601_202604__temporary_synovial_substitute__250099__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__temporary_synovial_substitute__250099__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-04T21:37:15</t>
+          <t>2026-04-14T21:55:16</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>67f63f417dbed89c13caba0d5872f06e980d9006e6052167e5ad0b78a21bff12</t>
+          <t>3ddeb6b35111a364e10807aa1997a8c2d49c7a61ef860e6438d89a02988618cd</t>
         </is>
       </c>
     </row>

--- a/hira_material_automation/output/monthly/202601_202604__temporary_synovial_substitute__250099__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202604__temporary_synovial_substitute__250099__normalized.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-04-14T21:55:16</t>
+          <t>2026-04-24T21:52:45</t>
         </is>
       </c>
     </row>
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3ddeb6b35111a364e10807aa1997a8c2d49c7a61ef860e6438d89a02988618cd</t>
+          <t>495cfca846214e96440786e2b185791920f8e168146f2e8913f8f778461a1369</t>
         </is>
       </c>
     </row>
